--- a/1 WonderEchoPro/附录/命令词播报词协议列表V3_中文_RAICOM比赛_精简.xlsx
+++ b/1 WonderEchoPro/附录/命令词播报词协议列表V3_中文_RAICOM比赛_精简.xlsx
@@ -1255,7 +1255,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J44"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="9" customWidth="1" style="1" min="1" max="1"/>
     <col width="19.3" customWidth="1" style="23" min="2" max="2"/>
@@ -1416,39 +1416,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>你好小虎</t>
-        </is>
-      </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>唤醒词</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="inlineStr">
-        <is>
-          <t>我在</t>
-        </is>
-      </c>
-      <c r="E5" s="26" t="inlineStr">
-        <is>
-          <t>主</t>
-        </is>
-      </c>
-      <c r="F5" s="27" t="inlineStr">
-        <is>
-          <t>AA 55 03 00 FB</t>
-        </is>
-      </c>
-      <c r="G5" s="27" t="inlineStr">
-        <is>
-          <t>AA 55 03 00 FB</t>
-        </is>
-      </c>
+      <c r="A5" s="26" t="n"/>
+      <c r="B5" s="27" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="27" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="27" t="n"/>
+      <c r="G5" s="27" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -1779,7 +1753,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B47"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="2.875" customWidth="1" style="23" min="1" max="1"/>
     <col width="103.875" customWidth="1" style="23" min="2" max="2"/>
